--- a/Project 0 - Exploratory Data Analysis/P0_EDA.xlsx
+++ b/Project 0 - Exploratory Data Analysis/P0_EDA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/niraj/Desktop/Supply Chain Analytics Portfolio/Excel Based/Project 0 - Exploratory Data Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/niraj/Desktop/Supply Chain Analytics Portfolio/Project 0 - Exploratory Data Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC9EC27-9803-6F4F-BCBE-F306DD5A0B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D015EF-27FF-5943-90DB-A3534BCA022F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" activeTab="7" xr2:uid="{C3EEE9E7-C4CC-B34A-858D-AAF02BA14B6F}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17160" xr2:uid="{C3EEE9E7-C4CC-B34A-858D-AAF02BA14B6F}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Rolling Trend" sheetId="7" r:id="rId7"/>
     <sheet name="CorrelationMatrix" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1596,10 +1596,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1621,39 +1618,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -1664,6 +1628,12 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
     </dxf>
     <dxf>
       <font>
@@ -9451,17 +9421,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B0F50C50-71DE-0C48-B41C-FC5604513ECA}" name="Table2" displayName="Table2" ref="A1:O366" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B0F50C50-71DE-0C48-B41C-FC5604513ECA}" name="Table2" displayName="Table2" ref="A1:O366" totalsRowShown="0" headerRowDxfId="8">
   <autoFilter ref="A1:O366" xr:uid="{B0F50C50-71DE-0C48-B41C-FC5604513ECA}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{25ADD1D4-51AB-5F44-8022-17141522CEB8}" name="d"/>
-    <tableColumn id="2" xr3:uid="{93743AF1-8707-114F-A293-52DB9FA4B37F}" name="date" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{93743AF1-8707-114F-A293-52DB9FA4B37F}" name="date" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{99C3921F-CE2A-7A47-AEF1-D55E16B2FE47}" name="wm_yr_wk"/>
-    <tableColumn id="4" xr3:uid="{711BB73B-1B30-1E4B-9458-D341E5C33518}" name="weekday" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{711BB73B-1B30-1E4B-9458-D341E5C33518}" name="weekday" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{7AB290D5-2291-7F4D-938C-EBB63CDD3D23}" name="wday"/>
     <tableColumn id="6" xr3:uid="{3B05A17D-F551-3A4F-AF32-1010EF0AE5B6}" name="month"/>
     <tableColumn id="7" xr3:uid="{DD99C55C-4AB3-204E-9A37-D81C73107186}" name="year"/>
-    <tableColumn id="8" xr3:uid="{B8B67994-C51E-C94A-ADD1-8177F75CFC66}" name="event_name_1" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{B8B67994-C51E-C94A-ADD1-8177F75CFC66}" name="event_name_1" dataDxfId="5"/>
     <tableColumn id="9" xr3:uid="{FC41465B-42E1-F240-9B29-62AB4677CE1D}" name="event_type_1"/>
     <tableColumn id="10" xr3:uid="{F17C027E-77EF-0B44-BC95-7C0F68D67C6A}" name="event_name_2"/>
     <tableColumn id="11" xr3:uid="{6C51100B-EAE2-2544-8E1F-0F1D301FA40F}" name="event_type_2"/>
@@ -9502,13 +9472,13 @@
     <tableColumn id="5" xr3:uid="{E9365784-1488-CA47-857D-2E6A19D2D783}" name="SKU3_Avg">
       <calculatedColumnFormula>AVERAGEIF(Table2[month],MonthlyPattern!A2,Table2[SKU3_Sales])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{6F5DF850-30AD-3C43-A63D-F0E418687237}" name="SKU_1_seasonality_Index" dataDxfId="9">
+    <tableColumn id="6" xr3:uid="{6F5DF850-30AD-3C43-A63D-F0E418687237}" name="SKU_1_seasonality_Index" dataDxfId="4">
       <calculatedColumnFormula>C2/AVERAGE(RawData!$M$2:$M$356)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{7A74C0F3-AD4F-9F41-8FFC-0D3B8E1A90A6}" name="SKU_2_seasonality_index" dataDxfId="8">
+    <tableColumn id="7" xr3:uid="{7A74C0F3-AD4F-9F41-8FFC-0D3B8E1A90A6}" name="SKU_2_seasonality_index" dataDxfId="3">
       <calculatedColumnFormula>D2/AVERAGE(RawData!$N$2:$N$356)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DBC91C20-5273-C34B-A298-19DD8CB04AC3}" name="SKU_3_seasonality_index" dataDxfId="7">
+    <tableColumn id="8" xr3:uid="{DBC91C20-5273-C34B-A298-19DD8CB04AC3}" name="SKU_3_seasonality_index" dataDxfId="2">
       <calculatedColumnFormula>E2/AVERAGE(RawData!$O$2:$O$356)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -27550,7 +27520,7 @@
         <v>0.74186991869918695</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:E14" si="2">C4/C9</f>
+        <f t="shared" ref="C14:D14" si="2">C4/C9</f>
         <v>1.1764705882352939</v>
       </c>
       <c r="D14">
@@ -27627,14 +27597,14 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:D9">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B2:D8">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:D9">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36694,6 +36664,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:D5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color theme="3" tint="0.499984740745262"/>
+        <color theme="9"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -36702,16 +36682,6 @@
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF7128"/>
-        <color theme="3" tint="0.499984740745262"/>
-        <color theme="9"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
